--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486516_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486516_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9557</v>
+        <v>3.551</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0565</v>
+        <v>2.4977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8992</v>
+        <v>1.0533</v>
       </c>
       <c r="G2" t="n">
         <v>2.7331</v>
@@ -610,13 +610,13 @@
         <v>0.435</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9403</v>
+        <v>0.5357</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8736</v>
+        <v>0.3149</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0667</v>
+        <v>0.2208</v>
       </c>
       <c r="V2" t="n">
         <v>0.9347</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.381</v>
+        <v>3.2464</v>
       </c>
       <c r="E3" t="n">
-        <v>1.232</v>
+        <v>3.8284</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1491</v>
+        <v>-0.5821</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4475</v>
+        <v>4.3596</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9702</v>
+        <v>-1.4599</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4773</v>
+        <v>5.8195</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1034</v>
+        <v>5.5981</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9886</v>
+        <v>-0.4102</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147</v>
+        <v>6.0084</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3442</v>
+        <v>-1.2386</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0184</v>
+        <v>-1.0497</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3626</v>
+        <v>-0.1889</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>1.151</v>
+        <v>-0.0877</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2161</v>
+        <v>-0.7246</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.06510000000000001</v>
+        <v>0.6369</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.243</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2723</v>
+        <v>1.9571</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9776</v>
+        <v>0.5614</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7054</v>
+        <v>1.3956</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3596</v>
+        <v>1.4475</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4599</v>
+        <v>0.9702</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8195</v>
+        <v>0.4773</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5981</v>
+        <v>1.1034</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4102</v>
+        <v>0.9886</v>
       </c>
       <c r="L4" t="n">
-        <v>6.0084</v>
+        <v>0.1147</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2386</v>
+        <v>0.3442</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0497</v>
+        <v>-0.0184</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1889</v>
+        <v>0.3626</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0618</v>
+        <v>0.727</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5754</v>
+        <v>0.5456</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.1815</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.243</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6021</v>
+        <v>1.4741</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2548</v>
+        <v>1.4351</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3473</v>
+        <v>0.039</v>
       </c>
       <c r="G5" t="n">
         <v>4.3296</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.432</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0769</v>
+        <v>0.1034</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6369</v>
+        <v>0.3287</v>
       </c>
       <c r="V5" t="n">
         <v>-1.9825</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6069</v>
+        <v>-1.7171</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1098</v>
+        <v>-2.3318</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4972</v>
+        <v>0.6147</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6572</v>
+        <v>1.5999</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6332</v>
+        <v>0.4804</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0239</v>
+        <v>1.1196</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6219</v>
+        <v>0.4597</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8514</v>
+        <v>0.3832</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2295</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0353</v>
+        <v>1.1402</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7819</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2534</v>
+        <v>1.0431</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6405</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5997</v>
+        <v>0.4711</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0187</v>
+        <v>0.1694</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4382</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4382</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8404</v>
+        <v>-2.024</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3318</v>
+        <v>-1.7118</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4914</v>
+        <v>-0.3122</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5999</v>
+        <v>-1.6572</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4804</v>
+        <v>-1.6332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1196</v>
+        <v>-0.0239</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4597</v>
+        <v>-0.6219</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3832</v>
+        <v>-0.8514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>0.2295</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1402</v>
+        <v>-1.0353</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.7819</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0431</v>
+        <v>-0.2534</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8276</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5172</v>
+        <v>0.2013</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4711</v>
+        <v>-0.0024</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0461</v>
+        <v>0.2037</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>-1.4382</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-1.4382</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7047</v>
+        <v>-3.2103</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.261</v>
+        <v>-2.3043</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4436</v>
+        <v>-0.906</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3697</v>
@@ -1078,13 +1078,13 @@
         <v>2.3926</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9728</v>
+        <v>0.4672</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1202</v>
+        <v>0.0769</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8526</v>
+        <v>0.3902</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6127</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8258</v>
+        <v>-3.5946</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3042</v>
+        <v>-4.8571</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4783</v>
+        <v>1.2626</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6884</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0376</v>
+        <v>0.2689</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9281</v>
+        <v>0.7123</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5959</v>
+        <v>-4.7027</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.0755</v>
+        <v>-6.3365</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4796</v>
+        <v>1.6338</v>
       </c>
       <c r="G10" t="n">
         <v>-5.5597</v>
@@ -1234,13 +1234,13 @@
         <v>2.6101</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0977</v>
+        <v>-0.2046</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5069</v>
+        <v>-0.7679</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4092</v>
+        <v>0.5633</v>
       </c>
       <c r="V10" t="n">
         <v>0.6264999999999999</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3626</v>
+        <v>-5.020099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.561399999999999</v>
+        <v>-9.218899999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>4.198700000000001</v>
+        <v>4.1987</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1947</v>
+        <v>2.194700000000002</v>
       </c>
       <c r="H11" t="n">
         <v>-5.2319</v>
@@ -1291,7 +1291,7 @@
         <v>1.2638</v>
       </c>
       <c r="L11" t="n">
-        <v>5.390899999999998</v>
+        <v>5.3909</v>
       </c>
       <c r="M11" t="n">
         <v>-4.459899999999999</v>
@@ -1312,10 +1312,10 @@
         <v>14.138</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6378</v>
+        <v>2.9803</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7688999999999997</v>
+        <v>-0.4264000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>3.4068</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3547</v>
+        <v>7.2719</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0485</v>
+        <v>5.7191</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3062</v>
+        <v>1.5528</v>
       </c>
       <c r="G12" t="n">
         <v>4.3704</v>
@@ -1390,13 +1390,13 @@
         <v>2.3926</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0157</v>
+        <v>-0.0985</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>-0.2199</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1252</v>
+        <v>0.1214</v>
       </c>
       <c r="V12" t="n">
         <v>1.695</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>P. ALI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3004</v>
+        <v>2.7996</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8409</v>
+        <v>1.5448</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4595</v>
+        <v>1.2548</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7441</v>
+        <v>-0.4845</v>
       </c>
       <c r="H13" t="n">
-        <v>1.694</v>
+        <v>0.216</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9499</v>
+        <v>-0.7004</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2917</v>
+        <v>-0.0302</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4814</v>
+        <v>0.7149</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1896</v>
+        <v>-0.7451</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5476</v>
+        <v>-0.4543</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2127</v>
+        <v>-0.4989</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7602</v>
+        <v>0.0446</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1457</v>
+        <v>-0.7159</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5312</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6145</v>
+        <v>-0.031</v>
       </c>
       <c r="V13" t="n">
-        <v>2.2806</v>
+        <v>2.2599</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2806</v>
+        <v>2.2599</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ALI</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.077</v>
+        <v>2.6685</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5448</v>
+        <v>0.3939</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5322</v>
+        <v>2.2746</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4845</v>
+        <v>0.7441</v>
       </c>
       <c r="H14" t="n">
-        <v>0.216</v>
+        <v>1.694</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7004</v>
+        <v>-0.9499</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0302</v>
+        <v>1.2917</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7149</v>
+        <v>1.4814</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7451</v>
+        <v>-0.1896</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4543</v>
+        <v>-0.5476</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4989</v>
+        <v>0.2127</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0446</v>
+        <v>-0.7602</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7401</v>
+        <v>-0.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4385</v>
+        <v>0.5137</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2465</v>
+        <v>0.4296</v>
       </c>
       <c r="V14" t="n">
-        <v>2.2599</v>
+        <v>2.2806</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2599</v>
+        <v>2.2806</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4314</v>
+        <v>1.1597</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5753</v>
+        <v>-0.5423</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8561</v>
+        <v>1.702</v>
       </c>
       <c r="G15" t="n">
         <v>-1.196</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8428</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2077</v>
+        <v>0.0901</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6351</v>
+        <v>0.481</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3904</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0286</v>
+        <v>-0.9768</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7029</v>
+        <v>-1.8811</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6744</v>
+        <v>0.9043</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0611</v>
+        <v>0.2247</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7311</v>
+        <v>0.4136</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.7922</v>
+        <v>-0.1889</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.033</v>
+        <v>0.365</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5519</v>
+        <v>0.365</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.5849</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0281</v>
+        <v>-0.1403</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1792</v>
+        <v>0.0486</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2073</v>
+        <v>-0.1889</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0102</v>
+        <v>-0.9617</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6249</v>
+        <v>-0.4614</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6351</v>
+        <v>-0.5002</v>
       </c>
       <c r="V16" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="X16" t="n">
         <v>-0.1952</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2311</v>
+        <v>-1.4062</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1046</v>
+        <v>-1.9265</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.5202</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2247</v>
+        <v>-1.0611</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4136</v>
+        <v>1.7311</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1889</v>
+        <v>-2.7922</v>
       </c>
       <c r="J17" t="n">
-        <v>0.365</v>
+        <v>-0.033</v>
       </c>
       <c r="K17" t="n">
-        <v>0.365</v>
+        <v>1.5519</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.5849</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1403</v>
+        <v>-1.0281</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0486</v>
+        <v>0.1792</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1889</v>
+        <v>-1.2073</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.216</v>
+        <v>-0.3674</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.8484</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.531</v>
+        <v>0.481</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1952</v>
+        <v>-0.1952</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1484</v>
+        <v>-1.7709</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9151</v>
+        <v>-2.6221</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2333</v>
+        <v>0.8512</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.4367</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1125</v>
+        <v>0.9156</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6805</v>
+        <v>-1.3523</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4166</v>
+        <v>1.221</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3285</v>
+        <v>1.068</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7451</v>
+        <v>0.153</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1514</v>
+        <v>-1.6576</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.216</v>
+        <v>-0.1523</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0645</v>
+        <v>-1.5053</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6679</v>
+        <v>-0.2466</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.411</v>
+        <v>-0.5804</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2569</v>
+        <v>0.3338</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6186</v>
+        <v>-1.975</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0691</v>
+        <v>-1.8033</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4505</v>
+        <v>-0.1716</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4367</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9156</v>
+        <v>0.1125</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3523</v>
+        <v>-0.6805</v>
       </c>
       <c r="J19" t="n">
-        <v>1.221</v>
+        <v>-0.4166</v>
       </c>
       <c r="K19" t="n">
-        <v>1.068</v>
+        <v>0.3285</v>
       </c>
       <c r="L19" t="n">
-        <v>0.153</v>
+        <v>-0.7451</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6576</v>
+        <v>-0.1514</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1523</v>
+        <v>-0.216</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5053</v>
+        <v>0.0645</v>
       </c>
       <c r="P19" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0944</v>
+        <v>-0.4945</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0274</v>
+        <v>-0.2992</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0669</v>
+        <v>-0.1953</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7743</v>
+        <v>-2.4082</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4166</v>
+        <v>-3.0813</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6422</v>
+        <v>0.6731</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7878</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.204</v>
+        <v>-0.8379</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.822</v>
+        <v>-0.4867</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.382</v>
+        <v>-0.3512</v>
       </c>
       <c r="V20" t="n">
         <v>1.13</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>5.362500000000001</v>
+        <v>5.3626</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.198800000000001</v>
+        <v>-4.1988</v>
       </c>
       <c r="F21" t="n">
-        <v>9.561300000000001</v>
+        <v>9.561400000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1949</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2319</v>
+        <v>5.231900000000001</v>
       </c>
       <c r="I21" t="n">
         <v>-7.4269</v>
@@ -2068,7 +2068,7 @@
         <v>4.460000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>6.495899999999999</v>
+        <v>6.495900000000001</v>
       </c>
       <c r="L21" t="n">
         <v>-2.0359</v>
@@ -2080,10 +2080,10 @@
         <v>-1.2638</v>
       </c>
       <c r="O21" t="n">
-        <v>-5.391100000000001</v>
+        <v>-5.3911</v>
       </c>
       <c r="P21" t="n">
-        <v>4.3502</v>
+        <v>4.350199999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-14.1379</v>
@@ -2092,13 +2092,13 @@
         <v>18.4883</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6378</v>
+        <v>-2.6377</v>
       </c>
       <c r="T21" t="n">
         <v>-3.4068</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7692</v>
+        <v>0.7690999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>5.8451</v>
